--- a/Data Analysis/HLOOKUP.xlsx
+++ b/Data Analysis/HLOOKUP.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,120 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+  <si>
+    <t>Product_ID</t>
+  </si>
+  <si>
+    <t>Product_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category </t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>Wireless Mouse</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>Bluetooth Speaker</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>Running Shoes</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>Coffee Mug</t>
+  </si>
+  <si>
+    <t>Kitchen</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>Office Chair</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>Backpack</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>LED Desk Lamp</t>
+  </si>
+  <si>
+    <t>Home Decor</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>Water Bottle</t>
+  </si>
+  <si>
+    <t>Sports</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>Smartphone Stand</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>Mechanical Keyboard</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -37,7 +145,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -45,12 +153,202 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -331,9 +629,170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="B1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.90625" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4">
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.989999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4">
+        <v>149.99</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="4">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="4">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6">
+        <v>89.99</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>